--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2019_los_rios.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2019_los_rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:48</t>
+    <t xml:space="preserve">2026-10-05 02:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>237113.41</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
